--- a/Docs/Missing Games (28 February 2026).xlsx
+++ b/Docs/Missing Games (28 February 2026).xlsx
@@ -8,29 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unofficial-RA-DATs\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A464F37-9AA5-4A31-971A-64A6A4A41DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43AC20CB-6260-423C-8C35-CD619B4A1760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1 - Sega Genesis" sheetId="1" r:id="rId1"/>
     <sheet name="3 - Super Nintendo" sheetId="2" r:id="rId2"/>
-    <sheet name="5 - Nintendo Game Boy Advance" sheetId="18" r:id="rId3"/>
-    <sheet name="7 - NES" sheetId="3" r:id="rId4"/>
-    <sheet name="8 - NEC TurboGrafx-16" sheetId="4" r:id="rId5"/>
-    <sheet name="11 - Sega Master System" sheetId="5" r:id="rId6"/>
-    <sheet name="12 - Sony Playstation" sheetId="12" r:id="rId7"/>
-    <sheet name="14 - SNK Neo Geo Pocket" sheetId="6" r:id="rId8"/>
-    <sheet name="15 - Sega Game Gear" sheetId="7" r:id="rId9"/>
-    <sheet name="16 - Nintendo GameCube" sheetId="15" r:id="rId10"/>
-    <sheet name="21 - Sony PlayStation 2" sheetId="8" r:id="rId11"/>
-    <sheet name="27 - Arcade" sheetId="9" r:id="rId12"/>
-    <sheet name="33 - Sega SG-1000" sheetId="10" r:id="rId13"/>
-    <sheet name="38 - Apple II" sheetId="13" r:id="rId14"/>
-    <sheet name="41 - Sony Playstation Portable" sheetId="11" r:id="rId15"/>
-    <sheet name="47 - NEC PC8801" sheetId="14" r:id="rId16"/>
-    <sheet name="Atari 7800" sheetId="16" r:id="rId17"/>
-    <sheet name="75 - Elektor TV Games Computer" sheetId="17" r:id="rId18"/>
+    <sheet name="7 - NES" sheetId="3" r:id="rId3"/>
+    <sheet name="8 - NEC TurboGrafx-16" sheetId="4" r:id="rId4"/>
+    <sheet name="11 - Sega Master System" sheetId="5" r:id="rId5"/>
+    <sheet name="12 - Sony Playstation" sheetId="12" r:id="rId6"/>
+    <sheet name="14 - SNK Neo Geo Pocket" sheetId="6" r:id="rId7"/>
+    <sheet name="15 - Sega Game Gear" sheetId="7" r:id="rId8"/>
+    <sheet name="16 - Nintendo GameCube" sheetId="15" r:id="rId9"/>
+    <sheet name="21 - Sony PlayStation 2" sheetId="8" r:id="rId10"/>
+    <sheet name="27 - Arcade" sheetId="9" r:id="rId11"/>
+    <sheet name="33 - Sega SG-1000" sheetId="10" r:id="rId12"/>
+    <sheet name="38 - Apple II" sheetId="13" r:id="rId13"/>
+    <sheet name="41 - Sony Playstation Portable" sheetId="11" r:id="rId14"/>
+    <sheet name="47 - NEC PC8801" sheetId="14" r:id="rId15"/>
+    <sheet name="Atari 7800" sheetId="16" r:id="rId16"/>
+    <sheet name="75 - Elektor TV Games Computer" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="639">
   <si>
     <t>GAME NAME</t>
   </si>
@@ -1959,15 +1958,6 @@
   </si>
   <si>
     <t>Can't find this rom. Was probably an old one.</t>
-  </si>
-  <si>
-    <t>f82b2f98c0c38191cc1f88b9a1df2678</t>
-  </si>
-  <si>
-    <t>Pokemon - Emerald/Pokemon - Recharged Yellow (v1.9.3) (Jaizu) (Hack)</t>
-  </si>
-  <si>
-    <t>Old Version. Can't find rom or patch.</t>
   </si>
 </sst>
 </file>
@@ -2453,43 +2443,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21206FC3-F148-4E8B-970C-C2D10F4AC196}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="58.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="24" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>609</v>
-      </c>
-      <c r="B2" t="s">
-        <v>610</v>
-      </c>
-      <c r="C2" t="s">
-        <v>611</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C33"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2868,7 +2821,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2910,7 +2863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2949,7 +2902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED3C4D5-8105-4AFE-8DDD-C1834B6448C4}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3030,7 +2983,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C369"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4964,7 +4917,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57818AC2-4463-4A09-8140-251C396204BF}">
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5035,7 +4988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{291E8787-1AD2-4F79-A006-551420ACFED6}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5073,7 +5026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C327077E-E26A-4D87-AB5A-C88905CE283A}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7178,43 +7131,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4644DD4-ED9F-4339-B0F0-912721685F47}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="65.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="33" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>640</v>
-      </c>
-      <c r="B3" t="s">
-        <v>639</v>
-      </c>
-      <c r="C3" t="s">
-        <v>641</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7274,7 +7190,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C53"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7874,7 +7790,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7924,7 +7840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12EA685A-6B74-42D3-8C63-E13E4551FD07}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7972,7 +7888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8022,7 +7938,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8059,4 +7975,41 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21206FC3-F148-4E8B-970C-C2D10F4AC196}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="58.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="24" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B2" t="s">
+        <v>610</v>
+      </c>
+      <c r="C2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>